--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -425,112 +425,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>VVOD</t>
+          <t>mtz1_pusk</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>KPONvnesh</t>
+          <t>mtz2_pusk</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>UAB</t>
+          <t>mtz3_pusk</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>UBC</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>UCA</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>kpon_pusk</t>
+          <t>blok</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E3" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
-      </c>
-      <c r="E4" t="n">
-        <v>50</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>1</v>
       </c>
     </row>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -425,28 +425,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>mtz1_pusk</t>
+          <t>VYVOD</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>mtz2_pusk</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mtz3_pusk</t>
+          <t>OVst</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>blok</t>
+          <t>NaSign</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>SV1vkl</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>SV2vkl</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>IB</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ICA</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>BNTpuskA</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>BNTpuskB</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>BNTpuskC</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>KZN1neipr</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>KPON1pusk</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>VNN1vkl</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>KZN2neipr</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>KPON2pusk</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>VNN2vkl</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>vvod</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>oper_vyvod</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mtzA_pusk</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>io_A</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mtzB_pusk</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>io_B</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mtzC_pusk</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>io_C</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>gen_pusk</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mtz_srabsign</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mtz_srab</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>kpon_pusk</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>set_changer</t>
         </is>
       </c>
     </row>
@@ -463,6 +618,99 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -472,10 +720,103 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -483,12 +824,105 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -497,18 +931,111 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -518,48 +1045,2988 @@
       </c>
       <c r="D6" t="n">
         <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV5"/>
+  <dimension ref="A1:BV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -902,11 +902,11 @@
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
+      <c r="K2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -920,14 +920,14 @@
       <c r="P2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
+      <c r="Q2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="n">
+        <v>50</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1099,38 +1099,38 @@
       <c r="A3" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
+      <c r="L3" s="1" t="n">
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1144,17 +1144,17 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
+      <c r="Q3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="S3" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1195,12 +1195,12 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="1" t="n">
+      <c r="AH3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
@@ -1294,8 +1294,8 @@
       <c r="BN3" t="n">
         <v>0</v>
       </c>
-      <c r="BO3" t="n">
-        <v>0</v>
+      <c r="BO3" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
         <v>0</v>
@@ -1316,454 +1316,6 @@
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
         <v>0</v>
       </c>
     </row>

--- a/test_results.xlsx
+++ b/test_results.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY3"/>
+  <dimension ref="A1:BV4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,35 +497,6 @@
     <col width="20" customWidth="1" min="72" max="72"/>
     <col width="20" customWidth="1" min="73" max="73"/>
     <col width="20" customWidth="1" min="74" max="74"/>
-    <col width="20" customWidth="1" min="75" max="75"/>
-    <col width="20" customWidth="1" min="76" max="76"/>
-    <col width="20" customWidth="1" min="77" max="77"/>
-    <col width="20" customWidth="1" min="78" max="78"/>
-    <col width="20" customWidth="1" min="79" max="79"/>
-    <col width="20" customWidth="1" min="80" max="80"/>
-    <col width="20" customWidth="1" min="81" max="81"/>
-    <col width="20" customWidth="1" min="82" max="82"/>
-    <col width="20" customWidth="1" min="83" max="83"/>
-    <col width="20" customWidth="1" min="84" max="84"/>
-    <col width="20" customWidth="1" min="85" max="85"/>
-    <col width="20" customWidth="1" min="86" max="86"/>
-    <col width="20" customWidth="1" min="87" max="87"/>
-    <col width="20" customWidth="1" min="88" max="88"/>
-    <col width="20" customWidth="1" min="89" max="89"/>
-    <col width="20" customWidth="1" min="90" max="90"/>
-    <col width="20" customWidth="1" min="91" max="91"/>
-    <col width="20" customWidth="1" min="92" max="92"/>
-    <col width="20" customWidth="1" min="93" max="93"/>
-    <col width="20" customWidth="1" min="94" max="94"/>
-    <col width="20" customWidth="1" min="95" max="95"/>
-    <col width="20" customWidth="1" min="96" max="96"/>
-    <col width="20" customWidth="1" min="97" max="97"/>
-    <col width="20" customWidth="1" min="98" max="98"/>
-    <col width="20" customWidth="1" min="99" max="99"/>
-    <col width="20" customWidth="1" min="100" max="100"/>
-    <col width="20" customWidth="1" min="101" max="101"/>
-    <col width="20" customWidth="1" min="102" max="102"/>
-    <col width="20" customWidth="1" min="103" max="103"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,7 +507,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>OV_lvttoc</t>
+          <t>OV</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -676,372 +647,227 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>KZN1neipr</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>VNN1vkl</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>KZN2neipr</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>VNN2vkl</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>OV_lvrbvtr1</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>vnesh_bnn_srab_lvrbvtr1</t>
-        </is>
-      </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>OV_lvrbvtr2</t>
+          <t>vvod_ptoc1</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>vnesh_bnn_srab_lvrbvtr2</t>
+          <t>oper_vyvod_ptoc1</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>OVlot</t>
+          <t>mtzA_pusk_ptoc1</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>OVlo</t>
+          <t>mtzB_pusk_ptoc1</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>OVzapv</t>
+          <t>mtzC_pusk_ptoc1</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>OVzavr</t>
+          <t>gen_pusk_ptoc1</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>vvod_lvrbvtr1</t>
+          <t>mtz_srabsign_ptoc1</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>oper_vyvod_lvrbvtr1</t>
+          <t>mtz_srab_ptoc1</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>u_lin_pusk_lvrbvtr1</t>
+          <t>io_A_ptoc1</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>u2_pusk_lvrbvtr1</t>
+          <t>io_B_ptoc1</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>pusk_lvrbvtr1</t>
+          <t>io_C_ptoc1</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>neispr_zn_lvrbvtr1</t>
+          <t>vvod_ptoc2</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>vvod_lvrbvtr2</t>
+          <t>oper_vyvod_ptoc2</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>oper_vyvod_lvrbvtr2</t>
+          <t>mtzA_pusk_ptoc2</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>u_lin_pusk_lvrbvtr2</t>
+          <t>mtzB_pusk_ptoc2</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>u2_pusk_lvrbvtr2</t>
+          <t>mtzC_pusk_ptoc2</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>pusk_lvrbvtr2</t>
+          <t>gen_pusk_ptoc2</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>neispr_zn_lvrbvtr2</t>
+          <t>mtz_srabsign_ptoc2</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>vvod_ptoc1_lvttoc</t>
+          <t>mtz_srab_ptoc2</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>oper_vyvod_ptoc1_lvttoc</t>
+          <t>io_A_ptoc2</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>mtzA_pusk_ptoc1_lvttoc</t>
+          <t>io_B_ptoc2</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>mtzB_pusk_ptoc1_lvttoc</t>
+          <t>io_C_ptoc2</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>mtzC_pusk_ptoc1_lvttoc</t>
+          <t>vvod_ptoc3</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>gen_pusk_ptoc_lvttoc</t>
+          <t>oper_vyvod_ptoc3</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>mtz_srabsign_ptoc1_lvttoc</t>
+          <t>mtzA_pusk_ptoc3</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>mtz_srab_ptoc1_lvttoc</t>
+          <t>mtzB_pusk_ptoc3</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>io_A_ptoc1_lvttoc</t>
+          <t>mtzC_pusk_ptoc3</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>io_B_ptoc1_lvttoc</t>
+          <t>gen_pusk_ptoc3</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>io_C_ptoc1_lvttoc</t>
+          <t>mtz_srabsign_ptoc3</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>vvod_ptoc2_lvttoc</t>
+          <t>mtz_srab_ptoc3</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>oper_vyvod_ptoc2_lvttoc</t>
+          <t>io_A_ptoc3</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>mtzA_pusk_ptoc2_lvttoc</t>
+          <t>io_B_ptoc3</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>mtzB_pusk_ptoc2_lvttoc</t>
+          <t>io_C_ptoc3</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>mtzC_pusk_ptoc2_lvttoc</t>
+          <t>kpon_pusk_ptuv1</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>gen_pusk_ptoc2_lvttoc</t>
+          <t>kpon_pusk_ptuv2</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>mtz_srabsign_ptoc2_lvttoc</t>
+          <t>ia_start_out_phar1</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>mtz_srab_ptoc2_lvttoc</t>
+          <t>ib_start_out_phar1</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>io_A_ptoc2_lvttoc</t>
+          <t>ic_start_out_phar1</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>io_B_ptoc2_lvttoc</t>
+          <t>start_phar1</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>io_C_ptoc2_lvttoc</t>
+          <t>blok_rblc1</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>vvod_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="BW1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="BX1" t="inlineStr">
-        <is>
-          <t>mtzA_pusk_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="BY1" t="inlineStr">
-        <is>
-          <t>mtzB_pusk_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>mtzC_pusk_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>gen_pusk_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>mtz_srabsign_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>mtz_srab_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>io_A_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>io_B_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>io_C_ptoc3_lvttoc</t>
-        </is>
-      </c>
-      <c r="CG1" t="inlineStr">
-        <is>
-          <t>kpon_pusk_ptuv1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>kpon_pusk_ptuv2_lvttoc</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>ia_start_out_phar1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>ib_start_out_phar1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>ic_start_out_phar1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>start_phar1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>blok_rblc1_lvttoc</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>mtz_pusk_lvttoc</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>vvod_ptrc1</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_ptrc1</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>pusk_ptrc1</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>srab_ptrc1</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>vvod_rblc1</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rblc1</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>zapret_rblc1</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>vvod_rbre1</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>oper_vyvod_rbre1</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>zapret_rbre1</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>pusk_lvalv</t>
+          <t>mtz_pusk</t>
         </is>
       </c>
     </row>
@@ -1079,8 +905,8 @@
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="n">
-        <v>5</v>
+      <c r="L2" t="n">
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -1145,8 +971,8 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
+      <c r="AH2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1199,57 +1025,57 @@
       <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="AZ2" s="1" t="n">
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
@@ -1266,93 +1092,6 @@
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1388,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1414,8 +1153,8 @@
       <c r="S3" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="T3" s="1" t="n">
-        <v>10</v>
+      <c r="T3" t="n">
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1456,8 +1195,8 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
+      <c r="AH3" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1510,57 +1249,57 @@
       <c r="AY3" t="n">
         <v>0</v>
       </c>
-      <c r="AZ3" s="1" t="n">
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
@@ -1579,92 +1318,229 @@
       <c r="BV3" t="n">
         <v>0</v>
       </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG3" s="1" t="n">
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="CH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CY3" t="n">
-        <v>0</v>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV4" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
